--- a/output/pdf_financials_xlsx/SHLE.xlsx
+++ b/output/pdf_financials_xlsx/SHLE.xlsx
@@ -1582,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.574</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -1597,10 +1597,10 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>32.717</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>19.901</v>
       </c>
     </row>
     <row r="35">
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.574</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>32.717</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>19.901</v>
       </c>
     </row>
     <row r="37">
@@ -2058,7 +2058,7 @@
         <v>5.455</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>13.119</v>
+        <v>8.545</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>2.554</v>
@@ -2073,10 +2073,10 @@
         <v>7.074</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>123.166</v>
+        <v>90.449</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>112.498</v>
+        <v>92.59699999999999</v>
       </c>
     </row>
     <row r="49">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -20302,11 +20302,7 @@
           <t>General &amp; administrative expense 19</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -23238,11 +23234,7 @@
           <t>General &amp; administrative expense 17</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -25541,11 +25533,7 @@
           <t>General &amp; administrative expense 18</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -26369,7 +26357,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -27689,7 +27677,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -28828,7 +28816,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E399" s="5" t="n">

--- a/output/pdf_financials_xlsx/SHLE.xlsx
+++ b/output/pdf_financials_xlsx/SHLE.xlsx
@@ -4219,22 +4219,22 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.841</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>2.373</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.511</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -14968,7 +14968,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
         <v>0.841</v>
       </c>
@@ -17317,7 +17321,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SHLE.xlsx
+++ b/output/pdf_financials_xlsx/SHLE.xlsx
@@ -2824,25 +2824,25 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.516</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>19.706</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>12.358</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>16.273</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>19.386</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>27.535</v>
       </c>
     </row>
     <row r="71">
@@ -2858,25 +2858,25 @@
         <v>33.692</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.516</v>
+        <v>1.032</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>19.706</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>7.5</v>
+        <v>19.858</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>17.561</v>
+        <v>33.834</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>8.093</v>
+        <v>27.479</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>11.69</v>
+        <v>39.225</v>
       </c>
     </row>
     <row r="72">
@@ -2994,25 +2994,25 @@
         <v>2.811</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>5.515</v>
+        <v>4.999</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>23.344</v>
+        <v>3.638</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>13.472</v>
+        <v>1.114</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>19.028</v>
+        <v>1.328</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>21.159</v>
+        <v>4.886</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>38.033</v>
+        <v>18.647</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>144.686</v>
+        <v>117.151</v>
       </c>
     </row>
     <row r="76">
@@ -3164,25 +3164,25 @@
         <v>0.4580672596477551</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.4839594834999639</v>
+        <v>0.4856531414729573</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.8973001720945868</v>
+        <v>0.9961717734773643</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.4457299966880321</v>
+        <v>0.4758250696487366</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.4298690798573905</v>
+        <v>0.4729733678817043</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.3874393617643048</v>
+        <v>0.4270685187710651</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.4747973854935806</v>
+        <v>0.5220075395974985</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.4305832822722511</v>
+        <v>0.4986139386871702</v>
       </c>
     </row>
     <row r="81">
@@ -4061,13 +4061,13 @@
         <v>0.143</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>-0.117</v>
+        <v>0.526</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>-0.289</v>
+        <v>0.658</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>-1.171</v>
+        <v>5.588</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>-5.218</v>
@@ -5949,7 +5949,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -7394,7 +7398,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12997,7 +13005,11 @@
           <t>Share-based compensation expense 16</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -13780,7 +13792,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -13839,7 +13855,11 @@
           <t>Share-based compensation expense 14</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -16290,7 +16310,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
